--- a/javascript/pruebaExcel.xlsx
+++ b/javascript/pruebaExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIO NO BORRAR\Documents\GitHub\asesores\javascript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DA1311-19D2-486F-A387-BDAF4B28F761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7140F3FD-5730-4EC3-A6FA-7C57C90A8346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{FD49C4A9-2D5E-4CF1-8EE0-4538EFDF560A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FD49C4A9-2D5E-4CF1-8EE0-4538EFDF560A}"/>
   </bookViews>
   <sheets>
     <sheet name="Postpago" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>titulo</t>
   </si>
@@ -204,12 +204,24 @@
   <si>
     <t>3 meses</t>
   </si>
+  <si>
+    <t>operador</t>
+  </si>
+  <si>
+    <t>verde</t>
+  </si>
+  <si>
+    <t>rojo</t>
+  </si>
+  <si>
+    <t>azul</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +248,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -257,13 +277,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,14 +619,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6621B904-7723-44C8-9556-80AFD06F28EE}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -618,8 +639,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -632,8 +656,11 @@
       <c r="D2">
         <v>99900</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -646,8 +673,11 @@
       <c r="D3">
         <v>59900</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -660,8 +690,11 @@
       <c r="D4">
         <v>69900</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -673,6 +706,9 @@
       </c>
       <c r="D5">
         <v>71991</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -685,14 +721,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B04FAA2-2FF3-4E25-9A2D-929EE39FA8B1}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -705,8 +741,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -719,8 +758,11 @@
       <c r="D2">
         <v>4500</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -733,8 +775,11 @@
       <c r="D3">
         <v>8500</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -747,8 +792,11 @@
       <c r="D4">
         <v>5000</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -760,6 +808,9 @@
       </c>
       <c r="D5">
         <v>5000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -772,13 +823,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B036406A-4D47-4197-B67D-9B10B3D8CA28}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -791,8 +842,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -805,8 +859,11 @@
       <c r="D2">
         <v>136900</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -819,8 +876,11 @@
       <c r="D3">
         <v>116900</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -833,8 +893,11 @@
       <c r="D4">
         <v>71495</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -847,8 +910,11 @@
       <c r="D5">
         <v>98910</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
     </row>
   </sheetData>
